--- a/data/trans_orig/P1408-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1408-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2007</t>
+          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13512</t>
+          <t>12808</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13823</t>
+          <t>13162</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>480552</t>
+          <t>481256</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>491251</t>
+          <t>491280</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>462817</t>
+          <t>461890</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>947730</t>
+          <t>948391</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>958073</t>
+          <t>958024</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14586</t>
+          <t>15080</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5642</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20161</t>
+          <t>20789</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11552</t>
+          <t>11993</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29185</t>
+          <t>29492</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>720903</t>
+          <t>720409</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>732326</t>
+          <t>731732</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>605333</t>
+          <t>604705</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>619852</t>
+          <t>619537</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1331797</t>
+          <t>1331490</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1349430</t>
+          <t>1348989</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13680</t>
+          <t>13838</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19092</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27739</t>
+          <t>28256</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>624988</t>
+          <t>624830</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>635637</t>
+          <t>635771</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>670652</t>
+          <t>670738</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>684391</t>
+          <t>684437</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1300673</t>
+          <t>1300156</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1318258</t>
+          <t>1317415</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7668</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24564</t>
+          <t>24500</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9009</t>
+          <t>8852</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24100</t>
+          <t>23925</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19670</t>
+          <t>20904</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42116</t>
+          <t>42759</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>494583</t>
+          <t>494647</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>511479</t>
+          <t>511134</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>491542</t>
+          <t>491717</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>506633</t>
+          <t>506790</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>992673</t>
+          <t>992030</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1015119</t>
+          <t>1013885</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>16499</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35193</t>
+          <t>35860</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17805</t>
+          <t>17200</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23997</t>
+          <t>23060</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46414</t>
+          <t>45797</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>351517</t>
+          <t>350850</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>370609</t>
+          <t>370211</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>386181</t>
+          <t>386786</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>399468</t>
+          <t>399518</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>744282</t>
+          <t>744899</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>766699</t>
+          <t>767636</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21396</t>
+          <t>21725</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42290</t>
+          <t>41611</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12319</t>
+          <t>12443</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28804</t>
+          <t>29199</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38921</t>
+          <t>38184</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>66288</t>
+          <t>63742</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250293</t>
+          <t>250972</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>271187</t>
+          <t>270858</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>314130</t>
+          <t>313735</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>330615</t>
+          <t>330491</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>569229</t>
+          <t>571775</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>596596</t>
+          <t>597333</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34080</t>
+          <t>34313</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58228</t>
+          <t>57841</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14982</t>
+          <t>14969</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35949</t>
+          <t>36125</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55277</t>
+          <t>55905</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85625</t>
+          <t>86844</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,97%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>151655</t>
+          <t>152042</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>175803</t>
+          <t>175570</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>297959</t>
+          <t>297783</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>318926</t>
+          <t>318939</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>458166</t>
+          <t>456947</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>488514</t>
+          <t>487886</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>115329</t>
+          <t>113437</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>158816</t>
+          <t>157978</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>74983</t>
+          <t>73793</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>111032</t>
+          <t>112672</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>200369</t>
+          <t>198466</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>258465</t>
+          <t>259841</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3117727</t>
+          <t>3118565</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3161214</t>
+          <t>3163106</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3268165</t>
+          <t>3266525</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3304214</t>
+          <t>3305404</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6397276</t>
+          <t>6395900</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6455372</t>
+          <t>6457275</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2012</t>
+          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,97 +3712,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>454146</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>428273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>430230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>882420</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>884376</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>682036</t>
+          <t>681331</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>604165</t>
+          <t>605961</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1291068</t>
+          <t>1289472</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10582</t>
+          <t>10723</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11395</t>
+          <t>11396</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17357</t>
+          <t>17275</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>671281</t>
+          <t>671140</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>679962</t>
+          <t>680018</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>698179</t>
+          <t>698178</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>707719</t>
+          <t>707702</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1374080</t>
+          <t>1374162</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1386603</t>
+          <t>1386652</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>17306</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12839</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>5937</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26271</t>
+          <t>23080</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>596512</t>
+          <t>597311</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>611712</t>
+          <t>611652</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>601425</t>
+          <t>601805</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>613180</t>
+          <t>613224</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1202609</t>
+          <t>1205800</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1223025</t>
+          <t>1222943</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>8396</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28302</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16479</t>
+          <t>16686</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15938</t>
+          <t>16032</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36058</t>
+          <t>37375</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>401127</t>
+          <t>403121</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>420829</t>
+          <t>421033</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>431321</t>
+          <t>431114</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>443453</t>
+          <t>443748</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>841171</t>
+          <t>839854</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>861291</t>
+          <t>861197</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>10948</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28274</t>
+          <t>28672</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12996</t>
+          <t>12064</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14734</t>
+          <t>15140</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35052</t>
+          <t>34852</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281512</t>
+          <t>281114</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>299433</t>
+          <t>298838</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>341000</t>
+          <t>341932</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>351064</t>
+          <t>351966</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>628730</t>
+          <t>628930</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>649048</t>
+          <t>648642</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19379</t>
+          <t>18955</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39887</t>
+          <t>38587</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>9873</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26329</t>
+          <t>25531</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33257</t>
+          <t>32663</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58526</t>
+          <t>60566</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>209964</t>
+          <t>211264</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>230472</t>
+          <t>230896</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>361467</t>
+          <t>362265</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>378927</t>
+          <t>377923</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>579121</t>
+          <t>577081</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>604390</t>
+          <t>604984</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>58749</t>
+          <t>56944</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>96904</t>
+          <t>93437</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>31756</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58750</t>
+          <t>58506</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>94290</t>
+          <t>95569</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>140732</t>
+          <t>139176</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3329875</t>
+          <t>3333342</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3368030</t>
+          <t>3369835</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3495166</t>
+          <t>3495410</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3523007</t>
+          <t>3522160</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6839962</t>
+          <t>6841518</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6886404</t>
+          <t>6885125</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2016</t>
+          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,62 +6726,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1954</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5894</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6097</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413535</t>
+          <t>413021</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>393879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>395755</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>809121</t>
+          <t>809324</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>7610</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10777</t>
+          <t>10930</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>583696</t>
+          <t>584502</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>555738</t>
+          <t>555934</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1143263</t>
+          <t>1143110</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1152088</t>
+          <t>1152138</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>919</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>10145</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,44 +7397,44 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3799</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8905</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
           <t>1,35%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3799</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8854</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>7</t>
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13634</t>
+          <t>14743</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>660091</t>
+          <t>658952</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>668177</t>
+          <t>668178</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,47 +7505,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,86%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>657587</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>652481</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>660403</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>99,43%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>98,65%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,86%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>657587</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>652532</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>660495</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>98,66%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1316849</t>
+          <t>1315740</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1327597</t>
+          <t>1327188</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14643</t>
+          <t>14606</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>9324</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19787</t>
+          <t>19264</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>631405</t>
+          <t>631442</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>642867</t>
+          <t>642928</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>639738</t>
+          <t>639753</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>648048</t>
+          <t>648068</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1275338</t>
+          <t>1275861</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1288900</t>
+          <t>1289875</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12087</t>
+          <t>12802</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30788</t>
+          <t>31438</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14531</t>
+          <t>14408</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16953</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39366</t>
+          <t>39711</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>447130</t>
+          <t>446480</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>465831</t>
+          <t>465116</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>482318</t>
+          <t>482441</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>493631</t>
+          <t>493667</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>935401</t>
+          <t>935056</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>957814</t>
+          <t>957623</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7844</t>
+          <t>7758</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22415</t>
+          <t>22004</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22336</t>
+          <t>22064</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18182</t>
+          <t>17793</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38305</t>
+          <t>38074</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>311915</t>
+          <t>312326</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>326486</t>
+          <t>326572</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>355426</t>
+          <t>355698</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>371502</t>
+          <t>370761</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>673787</t>
+          <t>674018</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>693910</t>
+          <t>694299</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11934</t>
+          <t>11343</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27450</t>
+          <t>27905</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8757</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25415</t>
+          <t>26085</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23686</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46514</t>
+          <t>47355</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>229548</t>
+          <t>229093</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>245064</t>
+          <t>245655</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>374754</t>
+          <t>374084</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>391412</t>
+          <t>391976</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>610653</t>
+          <t>609812</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>633481</t>
+          <t>633466</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51511</t>
+          <t>51201</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85453</t>
+          <t>83469</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32981</t>
+          <t>33464</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>61614</t>
+          <t>60705</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>92245</t>
+          <t>91677</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>135720</t>
+          <t>132478</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3308897</t>
+          <t>3310881</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3342839</t>
+          <t>3343149</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3482928</t>
+          <t>3483837</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3511561</t>
+          <t>3511078</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6803172</t>
+          <t>6806414</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6846647</t>
+          <t>6847215</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2023</t>
+          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21373</t>
+          <t>23045</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19944</t>
+          <t>21115</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>291827</t>
+          <t>290155</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310957</t>
+          <t>310992</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>693243</t>
+          <t>692072</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>710999</t>
+          <t>710971</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8033</t>
+          <t>8094</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12003</t>
+          <t>13407</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>3338</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15544</t>
+          <t>16075</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415514</t>
+          <t>415453</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>499501</t>
+          <t>498097</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509674</t>
+          <t>509683</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>919507</t>
+          <t>918976</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>931567</t>
+          <t>931713</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -10361,7 +10361,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7956</t>
+          <t>7803</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12002</t>
+          <t>12009</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528382</t>
+          <t>528535</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>534423</t>
+          <t>534295</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>540704</t>
+          <t>540556</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1066135</t>
+          <t>1066128</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1076028</t>
+          <t>1075696</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23080</t>
+          <t>24106</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7289</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18481</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13277</t>
+          <t>13439</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36195</t>
+          <t>35465</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>863631</t>
+          <t>862605</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>882609</t>
+          <t>882531</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>693857</t>
+          <t>694157</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>705049</t>
+          <t>705205</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1562854</t>
+          <t>1563584</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1585772</t>
+          <t>1585610</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11819</t>
+          <t>10993</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27529</t>
+          <t>25901</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>10545</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22384</t>
+          <t>22680</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25684</t>
+          <t>24610</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44445</t>
+          <t>44342</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>532708</t>
+          <t>534336</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>548418</t>
+          <t>549244</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>521081</t>
+          <t>520785</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>532466</t>
+          <t>532920</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1059257</t>
+          <t>1059360</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1078018</t>
+          <t>1079092</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17288</t>
+          <t>17259</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31990</t>
+          <t>31644</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28354</t>
+          <t>27957</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17927</t>
+          <t>17229</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54468</t>
+          <t>54868</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>335457</t>
+          <t>335803</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>350159</t>
+          <t>350188</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>578908</t>
+          <t>579305</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>600882</t>
+          <t>601254</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>920241</t>
+          <t>919841</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>956782</t>
+          <t>957480</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17483</t>
+          <t>17678</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31808</t>
+          <t>33488</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21186</t>
+          <t>21418</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35427</t>
+          <t>35451</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42321</t>
+          <t>42471</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62030</t>
+          <t>62714</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>250951</t>
+          <t>249271</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>265276</t>
+          <t>265081</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>389478</t>
+          <t>389454</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>403719</t>
+          <t>403487</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>645634</t>
+          <t>644950</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>665343</t>
+          <t>665193</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>63471</t>
+          <t>62876</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>102715</t>
+          <t>101720</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,82 +12086,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>88570</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>70208</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>108383</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
           <t>2,97%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>88570</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>71014</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>107790</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>172262</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>144396</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>201656</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
         <is>
           <t>2,42%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>172262</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>147277</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>200879</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3354311</t>
+          <t>3355306</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3393555</t>
+          <t>3394150</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,82 +12199,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>97,06%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>5198</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>3565904</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>3546091</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3584266</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>97,58%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
           <t>97,03%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>98,16%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>5198</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3565904</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>3546684</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3583460</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>98,08%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>8454</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>6939237</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>6909843</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>6967103</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
         <is>
           <t>97,58%</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>97,05%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>98,06%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>8454</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>6939237</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>6910620</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>6964222</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>97,58%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1408-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1408-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12808</t>
+          <t>12977</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13162</t>
+          <t>13944</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>481256</t>
+          <t>481087</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>491280</t>
+          <t>491272</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>461890</t>
+          <t>462133</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>948391</t>
+          <t>947609</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>958024</t>
+          <t>958050</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>3760</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15080</t>
+          <t>14837</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20789</t>
+          <t>19893</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11993</t>
+          <t>11982</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29492</t>
+          <t>30052</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>720409</t>
+          <t>720652</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>731732</t>
+          <t>731729</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>604705</t>
+          <t>605601</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>619537</t>
+          <t>619807</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1331490</t>
+          <t>1330930</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1348989</t>
+          <t>1349000</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13838</t>
+          <t>13304</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19006</t>
+          <t>17935</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>10810</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28256</t>
+          <t>27628</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>624830</t>
+          <t>625364</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>635771</t>
+          <t>635753</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>670738</t>
+          <t>671809</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>684437</t>
+          <t>684448</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1300156</t>
+          <t>1300784</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1317415</t>
+          <t>1317602</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>7826</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24500</t>
+          <t>24128</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8852</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23925</t>
+          <t>23836</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20904</t>
+          <t>19723</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42759</t>
+          <t>42178</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>494647</t>
+          <t>495019</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>511134</t>
+          <t>511321</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>491717</t>
+          <t>491806</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>506790</t>
+          <t>506604</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>992030</t>
+          <t>992611</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1013885</t>
+          <t>1015066</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16499</t>
+          <t>17080</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35860</t>
+          <t>34735</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17200</t>
+          <t>16850</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23060</t>
+          <t>24346</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45797</t>
+          <t>45508</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>350850</t>
+          <t>351975</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>370211</t>
+          <t>369630</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>386786</t>
+          <t>387136</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>399518</t>
+          <t>399962</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>744899</t>
+          <t>745188</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>767636</t>
+          <t>766350</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21725</t>
+          <t>21620</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41611</t>
+          <t>41457</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12443</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29199</t>
+          <t>29295</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38184</t>
+          <t>38990</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>63742</t>
+          <t>65128</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250972</t>
+          <t>251126</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>270858</t>
+          <t>270963</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>313735</t>
+          <t>313639</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>330491</t>
+          <t>330022</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>571775</t>
+          <t>570389</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>597333</t>
+          <t>596527</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,86%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34313</t>
+          <t>33918</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57841</t>
+          <t>57746</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14969</t>
+          <t>16196</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36125</t>
+          <t>35868</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55905</t>
+          <t>54238</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>86844</t>
+          <t>85981</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>152042</t>
+          <t>152137</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>175570</t>
+          <t>175965</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>297783</t>
+          <t>298040</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>318939</t>
+          <t>317712</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>456947</t>
+          <t>457810</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>487886</t>
+          <t>489553</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>90,03%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>113437</t>
+          <t>116127</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>157978</t>
+          <t>161980</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>73793</t>
+          <t>74356</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>112672</t>
+          <t>110814</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>198466</t>
+          <t>199435</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>259841</t>
+          <t>257911</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3118565</t>
+          <t>3114563</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3163106</t>
+          <t>3160416</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3266525</t>
+          <t>3268383</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3305404</t>
+          <t>3304841</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6395900</t>
+          <t>6397830</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6457275</t>
+          <t>6456306</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5756</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>681331</t>
+          <t>682053</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>605961</t>
+          <t>605344</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1289472</t>
+          <t>1290122</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10723</t>
+          <t>11012</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11396</t>
+          <t>10352</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17275</t>
+          <t>18177</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>671140</t>
+          <t>670851</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680018</t>
+          <t>679984</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>698178</t>
+          <t>699222</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>707702</t>
+          <t>707753</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1374162</t>
+          <t>1373260</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1386652</t>
+          <t>1386607</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17306</t>
+          <t>17702</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12459</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5937</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23080</t>
+          <t>23397</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>597311</t>
+          <t>596915</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>611652</t>
+          <t>612408</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>601805</t>
+          <t>600745</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>613224</t>
+          <t>613183</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1205800</t>
+          <t>1205483</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1222943</t>
+          <t>1222860</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>8755</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26308</t>
+          <t>27367</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16686</t>
+          <t>16617</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16032</t>
+          <t>15746</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37375</t>
+          <t>37270</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>403121</t>
+          <t>402062</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>421033</t>
+          <t>420674</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>431114</t>
+          <t>431183</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>443748</t>
+          <t>443511</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>839854</t>
+          <t>839959</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>861197</t>
+          <t>861483</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10948</t>
+          <t>10381</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28672</t>
+          <t>29081</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12064</t>
+          <t>12175</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15140</t>
+          <t>14318</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34852</t>
+          <t>34873</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281114</t>
+          <t>280705</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>298838</t>
+          <t>299405</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>341932</t>
+          <t>341821</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>351966</t>
+          <t>351945</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>628930</t>
+          <t>628909</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>648642</t>
+          <t>649464</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18955</t>
+          <t>19383</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38587</t>
+          <t>40072</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9873</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25531</t>
+          <t>25410</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32663</t>
+          <t>32124</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60566</t>
+          <t>58002</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>211264</t>
+          <t>209779</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>230896</t>
+          <t>230468</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>362265</t>
+          <t>362386</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>377923</t>
+          <t>377828</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>577081</t>
+          <t>579645</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>604984</t>
+          <t>605523</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>56944</t>
+          <t>55218</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>93437</t>
+          <t>91308</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,74 +6128,74 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>42468</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>30856</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>57667</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>116121</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>95606</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>141689</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>1,66%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>42468</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>31756</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>58506</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>116121</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>95569</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>139176</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
           <t>1,37%</t>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3333342</t>
+          <t>3335471</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3369835</t>
+          <t>3371561</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,77 +6241,77 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>3255</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>3511448</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>3496249</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3523060</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>98,81%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>98,38%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>6398</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>6864573</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>6839005</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>6885088</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>98,34%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>3255</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3511448</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>3495410</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3522160</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>98,35%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>6398</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>6864573</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>6841518</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>6885125</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413021</t>
+          <t>412462</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>809324</t>
+          <t>807908</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>7041</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>923</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7610</t>
+          <t>7608</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10930</t>
+          <t>11164</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>584502</t>
+          <t>583455</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>555934</t>
+          <t>555936</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>562622</t>
+          <t>562621</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1143110</t>
+          <t>1142876</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1152138</t>
+          <t>1152104</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>918</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10145</t>
+          <t>9158</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>980</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>9495</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>3083</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14743</t>
+          <t>13996</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>658952</t>
+          <t>659939</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>668178</t>
+          <t>668179</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>652481</t>
+          <t>651891</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>660403</t>
+          <t>660406</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1315740</t>
+          <t>1316487</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1327188</t>
+          <t>1327400</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14606</t>
+          <t>13885</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9324</t>
+          <t>9900</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19264</t>
+          <t>19126</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>631442</t>
+          <t>632163</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>642928</t>
+          <t>642895</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>639753</t>
+          <t>639177</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>648068</t>
+          <t>648063</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1275861</t>
+          <t>1275999</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1289875</t>
+          <t>1289084</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12802</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31438</t>
+          <t>32803</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>2333</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14408</t>
+          <t>14056</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17144</t>
+          <t>16514</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39711</t>
+          <t>39068</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>446480</t>
+          <t>445115</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>465116</t>
+          <t>465682</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>482441</t>
+          <t>482793</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>493667</t>
+          <t>494516</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>935056</t>
+          <t>935699</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>957623</t>
+          <t>958253</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7758</t>
+          <t>7738</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22004</t>
+          <t>22575</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22064</t>
+          <t>21327</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17793</t>
+          <t>17662</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38074</t>
+          <t>37637</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>312326</t>
+          <t>311755</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>326572</t>
+          <t>326592</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>355698</t>
+          <t>356435</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>370761</t>
+          <t>370910</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>674018</t>
+          <t>674455</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>694299</t>
+          <t>694430</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11343</t>
+          <t>12150</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27905</t>
+          <t>27275</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26085</t>
+          <t>26684</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23701</t>
+          <t>23375</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47355</t>
+          <t>46256</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>229093</t>
+          <t>229723</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>245655</t>
+          <t>244848</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>374084</t>
+          <t>373485</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>391976</t>
+          <t>391958</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>609812</t>
+          <t>610911</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>633466</t>
+          <t>633792</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51201</t>
+          <t>51915</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>83469</t>
+          <t>84355</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33464</t>
+          <t>31237</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60705</t>
+          <t>60482</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>91677</t>
+          <t>92622</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>132478</t>
+          <t>132714</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3310881</t>
+          <t>3309995</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3343149</t>
+          <t>3342435</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3483837</t>
+          <t>3484060</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3511078</t>
+          <t>3513305</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6806414</t>
+          <t>6806178</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6847215</t>
+          <t>6846270</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7969</t>
+          <t>8280</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23045</t>
+          <t>23538</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7969</t>
+          <t>8280</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21115</t>
+          <t>23952</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>305231</t>
+          <t>354232</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>290155</t>
+          <t>338974</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310992</t>
+          <t>360287</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>705218</t>
+          <t>762025</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>692072</t>
+          <t>746353</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>710971</t>
+          <t>768119</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -10018,12 +10018,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>8786</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5476</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13407</t>
+          <t>11847</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>7812</t>
+          <t>7912</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16075</t>
+          <t>15088</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -10121,27 +10121,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>421211</t>
+          <t>474511</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415453</t>
+          <t>468104</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>506028</t>
+          <t>495551</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>498097</t>
+          <t>489236</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509683</t>
+          <t>499078</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>927239</t>
+          <t>970061</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>918976</t>
+          <t>962885</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>931713</t>
+          <t>974807</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2538</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -10361,12 +10361,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>8909</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>849</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7542</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>2346</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12009</t>
+          <t>12235</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -10464,27 +10464,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>533971</t>
+          <t>618299</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528535</t>
+          <t>611928</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>538467</t>
+          <t>618057</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>534295</t>
+          <t>613946</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>540556</t>
+          <t>620639</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1072438</t>
+          <t>1236356</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1066128</t>
+          <t>1230090</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1075696</t>
+          <t>1239979</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078137</t>
+          <t>1242325</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078137</t>
+          <t>1242325</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078137</t>
+          <t>1242325</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>13509</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>7114</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24106</t>
+          <t>23621</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,17 +10729,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11749</t>
+          <t>12174</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>18807</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>24300</t>
+          <t>25684</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13439</t>
+          <t>17256</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35465</t>
+          <t>36735</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>874161</t>
+          <t>686010</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>862605</t>
+          <t>675898</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>882531</t>
+          <t>692405</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,17 +10842,17 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>700589</t>
+          <t>723613</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>694157</t>
+          <t>716980</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>705205</t>
+          <t>727903</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1574749</t>
+          <t>1409622</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1563584</t>
+          <t>1398571</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1585610</t>
+          <t>1418050</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>886711</t>
+          <t>699519</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>886711</t>
+          <t>699519</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>886711</t>
+          <t>699519</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712338</t>
+          <t>735787</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712338</t>
+          <t>735787</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712338</t>
+          <t>735787</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1599049</t>
+          <t>1435306</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1599049</t>
+          <t>1435306</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1599049</t>
+          <t>1435306</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18095</t>
+          <t>20351</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10993</t>
+          <t>12534</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25901</t>
+          <t>30257</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>15896</t>
+          <t>17918</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10545</t>
+          <t>11931</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22680</t>
+          <t>25658</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>33991</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24610</t>
+          <t>28789</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44342</t>
+          <t>50908</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>542142</t>
+          <t>588008</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>534336</t>
+          <t>578102</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>549244</t>
+          <t>595825</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>527569</t>
+          <t>587450</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>520785</t>
+          <t>579710</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>532920</t>
+          <t>593437</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1069711</t>
+          <t>1175457</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1059360</t>
+          <t>1162819</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1079092</t>
+          <t>1184938</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>543465</t>
+          <t>605368</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>543465</t>
+          <t>605368</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>543465</t>
+          <t>605368</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1103702</t>
+          <t>1213727</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1103702</t>
+          <t>1213727</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1103702</t>
+          <t>1213727</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24043</t>
+          <t>25621</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17259</t>
+          <t>18144</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31644</t>
+          <t>34834</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16457</t>
+          <t>18513</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>12907</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27957</t>
+          <t>25353</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>40500</t>
+          <t>44135</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17229</t>
+          <t>34953</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54868</t>
+          <t>55856</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>343404</t>
+          <t>380590</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>335803</t>
+          <t>371377</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>350188</t>
+          <t>388067</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>590805</t>
+          <t>419507</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>579305</t>
+          <t>412667</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>601254</t>
+          <t>425113</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>934209</t>
+          <t>800096</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>919841</t>
+          <t>788375</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>957480</t>
+          <t>809278</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607262</t>
+          <t>438020</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607262</t>
+          <t>438020</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607262</t>
+          <t>438020</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>974709</t>
+          <t>844231</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>974709</t>
+          <t>844231</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>974709</t>
+          <t>844231</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>24301</t>
+          <t>25596</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17678</t>
+          <t>18374</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33488</t>
+          <t>33978</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>27690</t>
+          <t>29970</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21418</t>
+          <t>22616</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35451</t>
+          <t>39389</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>51991</t>
+          <t>55566</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42471</t>
+          <t>44739</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62714</t>
+          <t>67198</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>258458</t>
+          <t>284602</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>249271</t>
+          <t>276220</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>265081</t>
+          <t>291824</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>397215</t>
+          <t>433669</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>389454</t>
+          <t>424250</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>403487</t>
+          <t>441023</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>655673</t>
+          <t>718272</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>644950</t>
+          <t>706640</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>665193</t>
+          <t>729099</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,22%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424905</t>
+          <t>463639</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424905</t>
+          <t>463639</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424905</t>
+          <t>463639</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707664</t>
+          <t>773838</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707664</t>
+          <t>773838</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707664</t>
+          <t>773838</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>83692</t>
+          <t>89995</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>62876</t>
+          <t>72487</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101720</t>
+          <t>107672</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>88570</t>
+          <t>95820</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>70208</t>
+          <t>81023</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>108383</t>
+          <t>113973</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>172262</t>
+          <t>185815</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>144396</t>
+          <t>159961</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>201656</t>
+          <t>211854</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3373334</t>
+          <t>3439813</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3355306</t>
+          <t>3422136</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3394150</t>
+          <t>3457321</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3565904</t>
+          <t>3632077</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3546091</t>
+          <t>3613924</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3584266</t>
+          <t>3646874</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6939237</t>
+          <t>7071891</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6909843</t>
+          <t>7045852</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6967103</t>
+          <t>7097745</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3457026</t>
+          <t>3529808</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3457026</t>
+          <t>3529808</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3457026</t>
+          <t>3529808</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3654474</t>
+          <t>3727897</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3654474</t>
+          <t>3727897</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3654474</t>
+          <t>3727897</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7111499</t>
+          <t>7257706</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7111499</t>
+          <t>7257706</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7111499</t>
+          <t>7257706</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
